--- a/docs/sdlc/70_delivery/WS2D-LI-001_OSSライセンス一覧.xlsx
+++ b/docs/sdlc/70_delivery/WS2D-LI-001_OSSライセンス一覧.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OSSライセンス一覧'!$A$1:$G$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ライセンス種別集計'!$A$1:$C$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'要確認（コピーレフト・不明）'!$A$1:$D$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ライセンス種別集計'!$A$1:$C$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'要確認（コピーレフト・不明）'!$A$1:$D$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +446,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MIT-0</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Apache-2.0 OR BSD-3-Clause</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>MIT License</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MIT AND PSF-2.0</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>BSD-3-Clause AND 0BSD AND MIT AND Zlib AND CC0-1.0</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Apache-2.0 OR BSD-2-Clause</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MIT-CMU</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>MIT License</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>BSD-2-Clause</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Mozilla Public License 2.0 (MPL 2.0)</t>
+          <t>MPL-2.0</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>PSF-2.0</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3087,10 +3087,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -3115,77 +3115,73 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MIT License</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MIT License</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Apache Software License</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BSD License</t>
+          <t>Apache Software License</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Mozilla Public License 2.0 (MPL 2.0)</t>
+          <t>BSD License</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>該当</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>BSD-2-Clause</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -3196,18 +3192,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BSD-3-Clause</t>
+          <t>Mozilla Public License 2.0 (MPL 2.0)</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>該当</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BSD-2-Clause</t>
+          <t>MIT-0</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -3218,7 +3218,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Python Software Foundation License</t>
+          <t>Apache-2.0 OR BSD-3-Clause</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -3229,7 +3229,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DFSG approved</t>
+          <t>Python Software Foundation License</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -3240,7 +3240,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Artistic License</t>
+          <t>MIT AND PSF-2.0</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -3248,8 +3248,89 @@
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BSD-3-Clause AND 0BSD AND MIT AND Zlib AND CC0-1.0</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Apache-2.0 OR BSD-2-Clause</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>MIT-CMU</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>MPL-2.0</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>該当</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>DFSG approved</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Artistic License</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PSF-2.0</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:C20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3260,13 +3341,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3348,7 +3429,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Mozilla Public License 2.0 (MPL 2.0)</t>
+          <t>MPL-2.0</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -3357,580 +3438,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>26.3.1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CacheControl</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>0.14.4</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>cffi</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2.1.0</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>click</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>8.4.2</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>cryptography</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>49.0.0</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Flask</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>3.1.3</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>greenlet</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>3.5.4</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>idna</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>iniconfig</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2.3.0</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>MarkupSafe</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>3.0.3</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>msgpack</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>1.2.1</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>mypy_extensions</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>1.1.0</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>numpy</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2.5.1</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>packaging</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>26.2</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>pillow</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>12.3.0</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>pip</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>26.2</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>playwright</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>1.61.0</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>pycparser</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Pygments</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2.20.0</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>pyparsing</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>3.3.2</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>pypdf</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>6.14.2</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>pytest</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>9.0.3</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>types-PyYAML</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>6.0.12.20260518</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>typing_extensions</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>4.16.0</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>urllib3</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>2.7.0</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Werkzeug</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>3.1.8</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>ライセンス特定が必要</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D30"/>
+  <autoFilter ref="A1:D4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>